--- a/tools/importer/reports/import-nedbank-homepage.report.xlsx
+++ b/tools/importer/reports/import-nedbank-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="303">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,874 @@
     <t>nedbank-homepage</t>
   </si>
   <si>
-    <t>2026-07-08T15:38:07.841Z</t>
+    <t>2026-07-09T13:07:19.759Z</t>
   </si>
   <si>
     <t>Make better money choices with us | Nedbank</t>
   </si>
   <si>
     <t>https://personal.nedbank.co.za/</t>
+  </si>
+  <si>
+    <t>insure/business-cover.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product","cards-checklist","columns-feature","cards-cover","cards-steps"]</t>
+  </si>
+  <si>
+    <t>insure/business-cover</t>
+  </si>
+  <si>
+    <t>product-detail-insurance</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:12:38.751Z</t>
+  </si>
+  <si>
+    <t>Is your business covered? | Nedbank Insurance</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/business-cover.html</t>
+  </si>
+  <si>
+    <t>insure/codi-what-it-is-and-what-you-need-to-know.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product","columns-feature","cards-cover"]</t>
+  </si>
+  <si>
+    <t>insure/codi-what-it-is-and-what-you-need-to-know</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:12:48.492Z</t>
+  </si>
+  <si>
+    <t>CODI: What it is and what you need to know | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/codi-what-it-is-and-what-you-need-to-know.html</t>
+  </si>
+  <si>
+    <t>insure/credit-life.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product","cards-cover"]</t>
+  </si>
+  <si>
+    <t>insure/credit-life</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:12:55.025Z</t>
+  </si>
+  <si>
+    <t>Debt? Make sure it’s covered with us | Nedbank Insurance</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/credit-life.html</t>
+  </si>
+  <si>
+    <t>insure/funeral-cover.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product"]</t>
+  </si>
+  <si>
+    <t>insure/funeral-cover</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:01.649Z</t>
+  </si>
+  <si>
+    <t>Looking for funeral insurance? Get cover from R30 | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/funeral-cover.html</t>
+  </si>
+  <si>
+    <t>insure/how-to-claim.report.json</t>
+  </si>
+  <si>
+    <t>["hero-product","columns-feature","cards-cover","cards-steps"]</t>
+  </si>
+  <si>
+    <t>insure/how-to-claim</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:11.191Z</t>
+  </si>
+  <si>
+    <t>Insurance claim forms | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/how-to-claim.html</t>
+  </si>
+  <si>
+    <t>insure/life-cover.report.json</t>
+  </si>
+  <si>
+    <t>["cards-steps"]</t>
+  </si>
+  <si>
+    <t>insure/life-cover</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:17.072Z</t>
+  </si>
+  <si>
+    <t>Protect your family when life happens | Nedbank Insurance</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/life-cover.html</t>
+  </si>
+  <si>
+    <t>insure/short-term-insurance.report.json</t>
+  </si>
+  <si>
+    <t>insure/short-term-insurance</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:25.066Z</t>
+  </si>
+  <si>
+    <t>Cover for all your assets? We’ve got you | Nedbank Insurance</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/short-term-insurance.html</t>
+  </si>
+  <si>
+    <t>insure/travel-insurance.report.json</t>
+  </si>
+  <si>
+    <t>insure/travel-insurance</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:33.718Z</t>
+  </si>
+  <si>
+    <t>Going places? Go with our travel insurance | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/insure/travel-insurance.html</t>
+  </si>
+  <si>
+    <t>learn/blog/5-reasons-not-to-withdraw-cash-from-a-credit-card.report.json</t>
+  </si>
+  <si>
+    <t>["columns-article","carousel-news"]</t>
+  </si>
+  <si>
+    <t>learn/blog/5-reasons-not-to-withdraw-cash-from-a-credit-card</t>
+  </si>
+  <si>
+    <t>blog-article</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:58:03.226Z</t>
+  </si>
+  <si>
+    <t>5 reasons not to withdraw cash from a credit card | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/5-reasons-not-to-withdraw-cash-from-a-credit-card.html</t>
+  </si>
+  <si>
+    <t>learn/blog/ai-and-future-of-banking.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/ai-and-future-of-banking</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:58:10.617Z</t>
+  </si>
+  <si>
+    <t>Enbi and AI: evolving the future of banking | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/ai-and-future-of-banking.html</t>
+  </si>
+  <si>
+    <t>learn/blog/atm-cash-withdrawals-on-phone.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/atm-cash-withdrawals-on-phone</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:58:18.384Z</t>
+  </si>
+  <si>
+    <t>Your cellphone is like a portable ATM | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/atm-cash-withdrawals-on-phone.html</t>
+  </si>
+  <si>
+    <t>learn/blog/avoid-early-withdrawal-on-your-retirement-savings.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/avoid-early-withdrawal-on-your-retirement-savings</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:59:11.359Z</t>
+  </si>
+  <si>
+    <t>Withdrawing retirement savings early is a bad idea | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/avoid-early-withdrawal-on-your-retirement-savings.html</t>
+  </si>
+  <si>
+    <t>learn/blog/bank-atm-cctv-footage.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/bank-atm-cctv-footage</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:59:20.220Z</t>
+  </si>
+  <si>
+    <t>ATM fraud: How long does the bank keep CCTV footage? | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/bank-atm-cctv-footage.html</t>
+  </si>
+  <si>
+    <t>learn/blog/banking-reimagined-go-digital.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/banking-reimagined-go-digital</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:59:28.511Z</t>
+  </si>
+  <si>
+    <t>Why going digital is now more important than ever | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/banking-reimagined-go-digital.html</t>
+  </si>
+  <si>
+    <t>learn/blog/benefits-of-tax-free-savings-and-investments.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/benefits-of-tax-free-savings-and-investments</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:59:36.626Z</t>
+  </si>
+  <si>
+    <t>Save more with tax-free investments | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/benefits-of-tax-free-savings-and-investments.html</t>
+  </si>
+  <si>
+    <t>learn/blog/better-money-choices-saves-on-banking-fees.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/better-money-choices-saves-on-banking-fees</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:59:45.535Z</t>
+  </si>
+  <si>
+    <t>4 better money choices to save on banking costs | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/better-money-choices-saves-on-banking-fees.html</t>
+  </si>
+  <si>
+    <t>learn/blog/boost-your-emergency-savings-with-greenbacks.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/boost-your-emergency-savings-with-greenbacks</t>
+  </si>
+  <si>
+    <t>2026-07-09T08:59:56.329Z</t>
+  </si>
+  <si>
+    <t>Building your emergency savings fund made easy | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/boost-your-emergency-savings-with-greenbacks.html</t>
+  </si>
+  <si>
+    <t>learn/blog/common-credit-card-scams.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/common-credit-card-scams</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:00:05.088Z</t>
+  </si>
+  <si>
+    <t>Protect yourself against credit card scams | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/common-credit-card-scams.html</t>
+  </si>
+  <si>
+    <t>learn/blog/double-your-money-fast.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/double-your-money-fast</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:00:14.034Z</t>
+  </si>
+  <si>
+    <t>How do I double my money fast? | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/double-your-money-fast.html</t>
+  </si>
+  <si>
+    <t>learn/blog/evolution-of-payments-and-future-of-credit-cards.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/evolution-of-payments-and-future-of-credit-cards</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:00:21.550Z</t>
+  </si>
+  <si>
+    <t>The future of credit cards | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/evolution-of-payments-and-future-of-credit-cards.html</t>
+  </si>
+  <si>
+    <t>learn/blog/funding-your-bank-account-so-it-stays-active.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/funding-your-bank-account-so-it-stays-active</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:00:30.797Z</t>
+  </si>
+  <si>
+    <t>How to fund your bank account so it stays active | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/funding-your-bank-account-so-it-stays-active.html</t>
+  </si>
+  <si>
+    <t>learn/blog/getting-business-payments-on-whatsapp.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/getting-business-payments-on-whatsapp</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:00:41.239Z</t>
+  </si>
+  <si>
+    <t>Money Message: Easy, secure payments via WhatsApp | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/getting-business-payments-on-whatsapp.html</t>
+  </si>
+  <si>
+    <t>learn/blog/greenbacks-levels.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/greenbacks-levels</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:00:53.026Z</t>
+  </si>
+  <si>
+    <t>Greenbacks updated: Enhanced rewards and new levels | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/greenbacks-levels.html</t>
+  </si>
+  <si>
+    <t>learn/blog/how-to-send-money-abroad.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/how-to-send-money-abroad</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:01:00.465Z</t>
+  </si>
+  <si>
+    <t>What you need to know about sending money abroad | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/how-to-send-money-abroad.html</t>
+  </si>
+  <si>
+    <t>learn/blog/insurance-advice-from-experts.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/insurance-advice-from-experts</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:01:08.972Z</t>
+  </si>
+  <si>
+    <t>Why it pays to get insurance advice from experts</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/insurance-advice-from-experts.html</t>
+  </si>
+  <si>
+    <t>learn/blog/investing-for-your-kids-to-retire-as-millionaires.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/investing-for-your-kids-to-retire-as-millionaires</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:01:17.439Z</t>
+  </si>
+  <si>
+    <t>Help your children retire as multimillionaires | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/investing-for-your-kids-to-retire-as-millionaires.html</t>
+  </si>
+  <si>
+    <t>learn/blog/is-it-worth-having-income-protection.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/is-it-worth-having-income-protection</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:01:28.624Z</t>
+  </si>
+  <si>
+    <t>Why is it worth having income protection? | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/is-it-worth-having-income-protection.html</t>
+  </si>
+  <si>
+    <t>learn/blog/manage-your-credit-score-on-the-money-app.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/manage-your-credit-score-on-the-money-app</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:01:41.484Z</t>
+  </si>
+  <si>
+    <t>How to monitor your credit score – for free! | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/manage-your-credit-score-on-the-money-app.html</t>
+  </si>
+  <si>
+    <t>learn/blog/manage-your-money-and-assets-in-your-home-country.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/manage-your-money-and-assets-in-your-home-country</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:01:51.692Z</t>
+  </si>
+  <si>
+    <t>Working abroad: Managing your taxes in South Africa | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/manage-your-money-and-assets-in-your-home-country.html</t>
+  </si>
+  <si>
+    <t>learn/blog/nedbank-migoals-understanding-account-change.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/nedbank-migoals-understanding-account-change</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:00.908Z</t>
+  </si>
+  <si>
+    <t>Your guide to Nedbank MiGoals account transitions| Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/nedbank-migoals-understanding-account-change.html</t>
+  </si>
+  <si>
+    <t>learn/blog/offshore-investments-as-part-of-wealth-building-strategy.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/offshore-investments-as-part-of-wealth-building-strategy</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:09.916Z</t>
+  </si>
+  <si>
+    <t>3 simple ways South Africans can invest offshore | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/offshore-investments-as-part-of-wealth-building-strategy.html</t>
+  </si>
+  <si>
+    <t>learn/blog/pay-your-bills-and-get-rewarded.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/pay-your-bills-and-get-rewarded</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:19.463Z</t>
+  </si>
+  <si>
+    <t>Pay your regular bills automatically and get rewards | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/pay-your-bills-and-get-rewarded.html</t>
+  </si>
+  <si>
+    <t>learn/blog/payshap-new-payment-method-fast-as-cash.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/payshap-new-payment-method-fast-as-cash</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:27.561Z</t>
+  </si>
+  <si>
+    <t>PayShap – A new payment method as fast as cash | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/payshap-new-payment-method-fast-as-cash.html</t>
+  </si>
+  <si>
+    <t>learn/blog/pick-the-perfect-bank-account.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/pick-the-perfect-bank-account</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:36.557Z</t>
+  </si>
+  <si>
+    <t>Picking the right bank account for your needs | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/pick-the-perfect-bank-account.html</t>
+  </si>
+  <si>
+    <t>learn/blog/power-of-saving-through-stokvel-account.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/power-of-saving-through-stokvel-account</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:45.349Z</t>
+  </si>
+  <si>
+    <t>Get the benefits of a Nedbank Stokvel Account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/power-of-saving-through-stokvel-account.html</t>
+  </si>
+  <si>
+    <t>learn/blog/receiving-international-payments-on-money-app.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/receiving-international-payments-on-money-app</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:52.994Z</t>
+  </si>
+  <si>
+    <t>The easy way to receive international payments | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/receiving-international-payments-on-money-app.html</t>
+  </si>
+  <si>
+    <t>learn/blog/reinvestment-for-growth.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/reinvestment-for-growth</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:02:59.842Z</t>
+  </si>
+  <si>
+    <t>Reinvest your returns for growth | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/reinvestment-for-growth.html</t>
+  </si>
+  <si>
+    <t>learn/blog/safe-payments-using-virtual-bank-cards.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/safe-payments-using-virtual-bank-cards</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:03:08.579Z</t>
+  </si>
+  <si>
+    <t>Virtual cards make online purchases more secure | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/safe-payments-using-virtual-bank-cards.html</t>
+  </si>
+  <si>
+    <t>learn/blog/saving-versus-investing.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/saving-versus-investing</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:03:21.027Z</t>
+  </si>
+  <si>
+    <t>How is saving different from investing? | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/saving-versus-investing.html</t>
+  </si>
+  <si>
+    <t>learn/blog/tap-on-phone-payments-for-business-owners.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/tap-on-phone-payments-for-business-owners</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:03:29.498Z</t>
+  </si>
+  <si>
+    <t>Traders: Accept tap-on-phone card payments anytime | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/tap-on-phone-payments-for-business-owners.html</t>
+  </si>
+  <si>
+    <t>learn/blog/top-questions-chatbot-enbi-is-asked.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/top-questions-chatbot-enbi-is-asked</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:03:39.624Z</t>
+  </si>
+  <si>
+    <t>The top questions Enbi gets asked | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/top-questions-chatbot-enbi-is-asked.html</t>
+  </si>
+  <si>
+    <t>learn/blog/travel-tips-from-thobi-rose.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/travel-tips-from-thobi-rose</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:03:49.694Z</t>
+  </si>
+  <si>
+    <t>5 top travel tips from Thobi Rose | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/travel-tips-from-thobi-rose.html</t>
+  </si>
+  <si>
+    <t>learn/blog/ways-to-invest-500-rand-monthly.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/ways-to-invest-500-rand-monthly</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:03:57.783Z</t>
+  </si>
+  <si>
+    <t>9 ways R500 a month can boost your savings | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/ways-to-invest-500-rand-monthly.html</t>
+  </si>
+  <si>
+    <t>learn/blog/why-nambitha-is-planning-for-retirement.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/why-nambitha-is-planning-for-retirement</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:04:11.377Z</t>
+  </si>
+  <si>
+    <t>Nambitha on why saving for retirement matters | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/why-nambitha-is-planning-for-retirement.html</t>
+  </si>
+  <si>
+    <t>learn/blog/why-your-will-is-so-important.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/why-your-will-is-so-important</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:04:23.119Z</t>
+  </si>
+  <si>
+    <t>Why you need a will: Get one drawn up for free | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/why-your-will-is-so-important.html</t>
+  </si>
+  <si>
+    <t>learn/blog/women-take-charge-of-your-financial-independence.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/women-take-charge-of-your-financial-independence</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:04:33.468Z</t>
+  </si>
+  <si>
+    <t>Women, take charge of your financial independence</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/women-take-charge-of-your-financial-independence.html</t>
+  </si>
+  <si>
+    <t>learn/blog/your-personal-details-on-the-dark-web.report.json</t>
+  </si>
+  <si>
+    <t>learn/blog/your-personal-details-on-the-dark-web</t>
+  </si>
+  <si>
+    <t>2026-07-09T09:04:41.925Z</t>
+  </si>
+  <si>
+    <t>Is your private data being traded on the Dark Web? | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/learn/blog/your-personal-details-on-the-dark-web.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/end-of-term/electronic-fixed-deposit/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>["cards-info","cards-checklist","cards-cta"]</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/end-of-term/electronic-fixed-deposit/ready-to-apply</t>
+  </si>
+  <si>
+    <t>application-form</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:43.134Z</t>
+  </si>
+  <si>
+    <t>How to open an Electronic Fixed-deposit Account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/end-of-term/electronic-fixed-deposit/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/end-of-term/tax-free-fixed-deposit/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/end-of-term/tax-free-fixed-deposit/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:49.047Z</t>
+  </si>
+  <si>
+    <t>Get a Tax-Free Fixed Deposit account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/end-of-term/tax-free-fixed-deposit/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/easy-access-deposit/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/easy-access-deposit/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:13:56.098Z</t>
+  </si>
+  <si>
+    <t>Open an EasyAccess Deposit Account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/in-24hrs/easy-access-deposit/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/justinvest/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/justinvest/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:14:03.185Z</t>
+  </si>
+  <si>
+    <t>Open a JustInvest account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/in-24hrs/justinvest/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/moneytrader/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/moneytrader/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:14:10.398Z</t>
+  </si>
+  <si>
+    <t>How to open a MoneyTrader account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/in-24hrs/moneytrader/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/platinuminvest/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/platinuminvest/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:14:15.685Z</t>
+  </si>
+  <si>
+    <t>How to open a Platinum Invest account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/in-24hrs/platinuminvest/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/tax-free-savings/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/in-24hrs/tax-free-savings/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:14:21.768Z</t>
+  </si>
+  <si>
+    <t>Open for a Tax-free Savings Account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/in-24hrs/tax-free-savings/ready-to-apply.html</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/on-demand/group-savings/ready-to-apply.report.json</t>
+  </si>
+  <si>
+    <t>["cards-info","cards-checklist"]</t>
+  </si>
+  <si>
+    <t>save-and-invest/accounts/on-demand/group-savings/ready-to-apply</t>
+  </si>
+  <si>
+    <t>2026-07-09T10:14:28.070Z</t>
+  </si>
+  <si>
+    <t>How to open a Group Savings Account | Nedbank</t>
+  </si>
+  <si>
+    <t>https://personal.nedbank.co.za/save-and-invest/accounts/on-demand/group-savings/ready-to-apply.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +1308,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="6" width="26" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +1366,1436 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" t="s">
+        <v>142</v>
+      </c>
+      <c r="G26" t="s">
+        <v>143</v>
+      </c>
+      <c r="H26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" t="s">
+        <v>147</v>
+      </c>
+      <c r="G27" t="s">
+        <v>148</v>
+      </c>
+      <c r="H27" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" t="s">
+        <v>162</v>
+      </c>
+      <c r="G30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" t="s">
+        <v>167</v>
+      </c>
+      <c r="G31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" t="s">
+        <v>173</v>
+      </c>
+      <c r="H32" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" t="s">
+        <v>177</v>
+      </c>
+      <c r="G33" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" t="s">
+        <v>191</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" t="s">
+        <v>192</v>
+      </c>
+      <c r="G36" t="s">
+        <v>193</v>
+      </c>
+      <c r="H36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" t="s">
+        <v>196</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>201</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" t="s">
+        <v>202</v>
+      </c>
+      <c r="G38" t="s">
+        <v>203</v>
+      </c>
+      <c r="H38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" t="s">
+        <v>207</v>
+      </c>
+      <c r="G39" t="s">
+        <v>208</v>
+      </c>
+      <c r="H39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" t="s">
+        <v>211</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" t="s">
+        <v>212</v>
+      </c>
+      <c r="G40" t="s">
+        <v>213</v>
+      </c>
+      <c r="H40" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" t="s">
+        <v>216</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" t="s">
+        <v>217</v>
+      </c>
+      <c r="G41" t="s">
+        <v>218</v>
+      </c>
+      <c r="H41" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F42" t="s">
+        <v>222</v>
+      </c>
+      <c r="G42" t="s">
+        <v>223</v>
+      </c>
+      <c r="H42" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" t="s">
+        <v>228</v>
+      </c>
+      <c r="H43" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>230</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>231</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>66</v>
+      </c>
+      <c r="F44" t="s">
+        <v>232</v>
+      </c>
+      <c r="G44" t="s">
+        <v>233</v>
+      </c>
+      <c r="H44" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>235</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>66</v>
+      </c>
+      <c r="F45" t="s">
+        <v>237</v>
+      </c>
+      <c r="G45" t="s">
+        <v>238</v>
+      </c>
+      <c r="H45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" t="s">
+        <v>242</v>
+      </c>
+      <c r="G46" t="s">
+        <v>243</v>
+      </c>
+      <c r="H46" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>245</v>
+      </c>
+      <c r="B47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>66</v>
+      </c>
+      <c r="F47" t="s">
+        <v>247</v>
+      </c>
+      <c r="G47" t="s">
+        <v>248</v>
+      </c>
+      <c r="H47" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>250</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
+        <v>251</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>66</v>
+      </c>
+      <c r="F48" t="s">
+        <v>252</v>
+      </c>
+      <c r="G48" t="s">
+        <v>253</v>
+      </c>
+      <c r="H48" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>255</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
+        <v>256</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>66</v>
+      </c>
+      <c r="F49" t="s">
+        <v>257</v>
+      </c>
+      <c r="G49" t="s">
+        <v>258</v>
+      </c>
+      <c r="H49" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>260</v>
+      </c>
+      <c r="B50" t="s">
+        <v>261</v>
+      </c>
+      <c r="C50" t="s">
+        <v>262</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>263</v>
+      </c>
+      <c r="F50" t="s">
+        <v>264</v>
+      </c>
+      <c r="G50" t="s">
+        <v>265</v>
+      </c>
+      <c r="H50" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>267</v>
+      </c>
+      <c r="B51" t="s">
+        <v>261</v>
+      </c>
+      <c r="C51" t="s">
+        <v>268</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>263</v>
+      </c>
+      <c r="F51" t="s">
+        <v>269</v>
+      </c>
+      <c r="G51" t="s">
+        <v>270</v>
+      </c>
+      <c r="H51" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>272</v>
+      </c>
+      <c r="B52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" t="s">
+        <v>273</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>263</v>
+      </c>
+      <c r="F52" t="s">
+        <v>274</v>
+      </c>
+      <c r="G52" t="s">
+        <v>275</v>
+      </c>
+      <c r="H52" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>277</v>
+      </c>
+      <c r="B53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C53" t="s">
+        <v>278</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>263</v>
+      </c>
+      <c r="F53" t="s">
+        <v>279</v>
+      </c>
+      <c r="G53" t="s">
+        <v>280</v>
+      </c>
+      <c r="H53" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>282</v>
+      </c>
+      <c r="B54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" t="s">
+        <v>283</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>263</v>
+      </c>
+      <c r="F54" t="s">
+        <v>284</v>
+      </c>
+      <c r="G54" t="s">
+        <v>285</v>
+      </c>
+      <c r="H54" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>287</v>
+      </c>
+      <c r="B55" t="s">
+        <v>261</v>
+      </c>
+      <c r="C55" t="s">
+        <v>288</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>263</v>
+      </c>
+      <c r="F55" t="s">
+        <v>289</v>
+      </c>
+      <c r="G55" t="s">
+        <v>290</v>
+      </c>
+      <c r="H55" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>292</v>
+      </c>
+      <c r="B56" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" t="s">
+        <v>293</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>263</v>
+      </c>
+      <c r="F56" t="s">
+        <v>294</v>
+      </c>
+      <c r="G56" t="s">
+        <v>295</v>
+      </c>
+      <c r="H56" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>297</v>
+      </c>
+      <c r="B57" t="s">
+        <v>298</v>
+      </c>
+      <c r="C57" t="s">
+        <v>299</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>263</v>
+      </c>
+      <c r="F57" t="s">
+        <v>300</v>
+      </c>
+      <c r="G57" t="s">
+        <v>301</v>
+      </c>
+      <c r="H57" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
